--- a/generated/08_merge.xlsx
+++ b/generated/08_merge.xlsx
@@ -561,7 +561,7 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="2" min="0" max="16383" man="1"/>
   </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -596,6 +596,6 @@
   <rowBreaks count="1" manualBreakCount="1">
     <brk id="2" min="0" max="16383" man="1"/>
   </rowBreaks>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
 </worksheet>
 </file>